--- a/i18n/pt.xlsx
+++ b/i18n/pt.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -3806,9 +3806,6 @@
     <t>Empates valem.</t>
   </si>
   <si>
-    <t>Conte o número de aves que você jogou no habitat em que você jogou menos aves. Mesmo se você possuir dois habitats empatados por menos aves, você pode pontuar esse bônus. Por exemplo, se todos os seus habitats tiverem 3 aves neles, seu habitat com menos aves  tem 3 aves.</t>
-  </si>
-  <si>
     <t>Enclosure Builder</t>
   </si>
   <si>
@@ -4202,57 +4199,6 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Comida no estoque pessoal</t>
   </si>
   <si>
@@ -4271,9 +4217,6 @@
     <t>O número de cartas de ave na sua mão</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
     <t>Aves que valem mais de 4 pontos</t>
   </si>
   <si>
@@ -4283,18 +4226,12 @@
     <t>O número de aves que você possui com um valor impresso de mais de 4 pontos</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Aves sem nenhum ovo</t>
   </si>
   <si>
     <t>O número de aves que você possui que não tenham nenhum ovo sobre elas quando este objetivo for pontuado</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Aves em uma linha</t>
   </si>
   <si>
@@ -4304,18 +4241,12 @@
     <t>O número de aves que você possui no habitat com mais aves</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>Colunas preenchidas</t>
   </si>
   <si>
     <t>O número de colunas onde todos os três espaços estejam preenchidos</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Poderes marrons</t>
   </si>
   <si>
@@ -4325,36 +4256,24 @@
     <t>O número de aves que você possui que tenham poderes marrons "quando ativado"</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
     <t>Poderes brancos &amp; sem poderes</t>
   </si>
   <si>
     <t>O número de aves que você possui que tenham um poder "quando jogado", ou não tenham poder</t>
   </si>
   <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
     <t>[flocking] com cartas embaixo</t>
   </si>
   <si>
     <t>O número de aves que você possui que tenham pelo menos 1 carta enfiada embaixo delas</t>
   </si>
   <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
     <t>Custo em comida das aves jogadas</t>
   </si>
   <si>
     <t>Conte o custo em comida de suas aves, lembrando de contar apenas 1 comida para aves que tenham uma escolha em seus custos de comida</t>
   </si>
   <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Invertebrados no custo em comida das suas aves</t>
   </si>
   <si>
@@ -4362,9 +4281,6 @@
   </si>
   <si>
     <t>Conte a quantidade de símbolos da comida dessa peça de objetivo que aparecem nos custos em comida das suas cartas de ave. Por exemplo, para o objetivo “[fruit] + [seed] no custo em comida das suas aves”, olhe os custos em comida no canto superior esquerdo das aves que você jogou em seu tabuleiro, e conte todos os [fruit] mais todos os [seed]. Se uma ave tiver um custo “[fruit]/[seed]” (você paga um OU um para jogar a ave), ele conta como apenas uma comida para este objetivo de final de rodada. Não conte [wild] ou [nectar].</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
   </si>
   <si>
     <t>Frutas + sementes no custo em comida das suas aves</t>
@@ -4375,7 +4291,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[fruit] + [seed] </t>
     </r>
@@ -4384,13 +4301,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>no custo em comida das suas aves</t>
     </r>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
   </si>
   <si>
     <t>Roedores + peixes no custo em comida das suas aves</t>
@@ -4401,7 +4316,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[rodent] + [fish] </t>
     </r>
@@ -4410,15 +4326,13 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>no custo em comida das suas aves</t>
     </r>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Sem objetivo</t>
   </si>
   <si>
@@ -4428,9 +4342,6 @@
     <t>Não pontue um objetivo no final desta rodada. Mantenha seu cubo. Todas as rodadas seguintes terão 1 cubo a mais do que normalmente teria.</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Bico para a esquerda</t>
   </si>
   <si>
@@ -4440,18 +4351,12 @@
     <t>Estes objetivos contam cartas que mostram uma ave cujo bico está apontando na direção indicada. Aves cujos bicos estão apontando diretamente para frente (ou para cima) não contam para nenhum destes objetivos.&lt;br&gt;Esses objetivos foram adicionados para dar aos jogadores outra razão para olhar atentamente para a arte. Apesar de termos avaliado todas as cartas e concluído que a direção do bico não seria muito difícil de determinar, se sua mesa tiver problemas com isso, fique à vontade para deixar essa peça fora do jogo. Existem algumas aves que precisam de esclarecimentos:&lt;br&gt;&lt;ul&gt;&lt;li&gt;O Wrybill, apesar de estar olhando para frente, tem um bico que está apontando para o lado esquerdo da carta.&lt;/li&gt;&lt;li&gt;A carta Common Loon (do jogo base) e a carta Little Grebe (da Expansão Asia) tem 1 ave apontando para cada direção, portanto ela se qualifica para ambos os objetivos.&lt;/li&gt;&lt;li&gt;A carta Great Crested Grebe (da Expansão Europa) tem 2 aves apontando para a mesma direção: ela conta como uma única carta que tem uma ave que está apontando para a esquerda.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Aqui está uma lista com as aves que não estão apontando para a direita e nem para a esquerda.&lt;br&gt;&lt;b&gt;Jogo Base&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Barn Owl&lt;/li&gt;&lt;li&gt;Barred Owl&lt;/li&gt;&lt;li&gt;Burrowing Owl&lt;/li&gt;&lt;li&gt;California Condor&lt;/li&gt;&lt;li&gt;Eastern Screech-Owl&lt;/li&gt;&lt;li&gt;Great Horned Owl&lt;/li&gt;&lt;li&gt;Horned Lark&lt;/li&gt;&lt;li&gt;Spotted Owl&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Europa&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Little Owl&lt;/li&gt;&lt;li&gt;Snowy Owl&lt;/li&gt;&lt;li&gt;Short-Toed Treecreeper&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Oceania&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Australian Owlet-Nightjar&lt;/li&gt;&lt;li&gt;Kākāpō&lt;/li&gt;&lt;li&gt;Rufous Owl&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Asia&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Bearded Reedling&lt;/li&gt;&lt;li&gt;Eurasian Eagle-Owl&lt;/li&gt;&lt;li&gt;Forest Owlet&lt;/li&gt;&lt;li&gt;Oriental Bay-Owl&lt;/li&gt;&lt;li&gt;Spoon-Billed Sandpiper&lt;/li&gt;&lt;li&gt;Sri Lanka Frogmouth&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Bico para a direita</t>
   </si>
   <si>
     <t>[beak-right] bico para a direita</t>
   </si>
   <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
     <t>Cubos em “Jogar Ave”</t>
   </si>
   <si>
@@ -4461,75 +4366,36 @@
     <t>Conte a quantidade de cubos que você colocou em “Jogar Ave” nesta rodada. Note que este objetivo requer que você mantenha os cubos nas linhas onde você os jogou.</t>
   </si>
   <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
     <t>[bird] que valem ≤3[point]</t>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
     <t>[duet-token] EM [bowl][cavity][ground][platform]</t>
   </si>
   <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
     <t>[duet-token] EM [fish][fruit][rodent][seed][invertebrate]</t>
   </si>
   <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
     <t>[duet-token] QUE NÃO ESTEJAM NA BORDA DO MAPA</t>
   </si>
   <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
     <t>[duet-token] QUE ESTEJAM NA BORDA DO MAPA</t>
   </si>
   <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
     <t>[duet-token] EM UMA LINHA HORIZONTAL QUALQUER</t>
   </si>
   <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
     <t>MENOS [duet-token] EM ESPAÇOS DE BÔNUS</t>
   </si>
   <si>
-    <t>In Forest</t>
-  </si>
-  <si>
     <t>[duet-token] EM [forest]</t>
   </si>
   <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
     <t>[duet-token] EM [grassland]</t>
   </si>
   <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
     <t>[duet-token] EM [wetland]</t>
   </si>
   <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>TOTAL DE [duet-token] NO MAPA</t>
   </si>
   <si>
@@ -4609,6 +4475,144 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Conte o número de aves que você jogou no habitat em que você jogou menos aves. Mesmo se você possuir dois habitats empatados por menos aves, você pode pontuar esse bônus. Por exemplo, se todos os seus habitats tiverem 3 aves neles, seu habitat com menos aves tem 3 aves.</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -4644,18 +4648,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -4663,6 +4663,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4700,7 +4707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -4738,6 +4745,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5088,7 +5096,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>1513</v>
+        <v>1467</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -5281,7 +5289,7 @@
         <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1510</v>
+        <v>1464</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>20</v>
@@ -5811,7 +5819,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>1503</v>
+        <v>1457</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>120</v>
@@ -7377,7 +7385,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1504</v>
+        <v>1458</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>316</v>
@@ -8109,7 +8117,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1506</v>
+        <v>1460</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>406</v>
@@ -8942,7 +8950,7 @@
         <v>510</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1507</v>
+        <v>1461</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>13</v>
@@ -11520,7 +11528,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="20" t="s">
-        <v>1509</v>
+        <v>1463</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>816</v>
@@ -11785,7 +11793,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>1505</v>
+        <v>1459</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>861</v>
@@ -12467,7 +12475,7 @@
         <v>700</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>1511</v>
+        <v>1465</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>739</v>
@@ -13608,7 +13616,7 @@
         <v>1100</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>1508</v>
+        <v>1462</v>
       </c>
       <c r="D399" s="5" t="s">
         <v>1010</v>
@@ -13827,7 +13835,7 @@
         <v>1010</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>1512</v>
+        <v>1466</v>
       </c>
       <c r="I410" s="8" t="s">
         <v>20</v>
@@ -14899,7 +14907,7 @@
         <v>1230</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1257</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -14907,25 +14915,25 @@
         <v>1011</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>1260</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>1261</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -14933,22 +14941,22 @@
         <v>1012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>1264</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>1265</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="G14" s="12" t="s">
         <v>1266</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>1267</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -14957,16 +14965,16 @@
         <v>1013</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="10" t="s">
         <v>1269</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>1270</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="10" t="s">
@@ -14981,20 +14989,20 @@
         <v>1014</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="10" t="s">
         <v>1272</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>1273</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="10" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -15003,16 +15011,16 @@
         <v>1015</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="10" t="s">
         <v>1276</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>1277</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="10" t="s">
@@ -15025,23 +15033,23 @@
         <v>1016</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="10" t="s">
         <v>1279</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>1280</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="10" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>1281</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15055,19 +15063,19 @@
         <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>1283</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
         <v>1284</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>1285</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>1230</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15075,23 +15083,23 @@
         <v>1018</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="10" t="s">
         <v>1288</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>1289</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="10" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>1290</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15099,25 +15107,25 @@
         <v>1019</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="10" t="s">
         <v>1293</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>1294</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>1295</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15125,19 +15133,19 @@
         <v>1020</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="10" t="s">
         <v>1297</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="10" t="s">
         <v>1298</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>1299</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>1230</v>
@@ -15149,23 +15157,23 @@
         <v>1021</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="10" t="s">
         <v>1301</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>1302</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>1303</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15173,23 +15181,23 @@
         <v>1022</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="10" t="s">
         <v>1306</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>1307</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="10" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15203,19 +15211,19 @@
         <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>1309</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="F25" s="10" t="s">
         <v>1310</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="G25" s="10" t="s">
         <v>1311</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="H25" s="13" t="s">
         <v>1312</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15223,25 +15231,25 @@
         <v>1024</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="F26" s="10" t="s">
         <v>1316</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>1317</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15249,23 +15257,23 @@
         <v>1025</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="10" t="s">
         <v>1319</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>1320</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="10" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15273,16 +15281,16 @@
         <v>1026</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="10" t="s">
         <v>1322</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>1323</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="10" t="s">
@@ -15295,23 +15303,23 @@
         <v>1027</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="10" t="s">
         <v>1325</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>1326</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="10" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>1327</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15319,16 +15327,16 @@
         <v>1028</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="10" t="s">
         <v>1330</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>1331</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="10" t="s">
@@ -15341,23 +15349,23 @@
         <v>1029</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="10" t="s">
         <v>1333</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>1334</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="10" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15365,25 +15373,25 @@
         <v>1030</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="10" t="s">
         <v>1337</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="F32" s="10" t="s">
         <v>1338</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>1339</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15391,22 +15399,22 @@
         <v>1032</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>1341</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="11" t="s">
         <v>1342</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="G33" s="10" t="s">
         <v>1343</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>1344</v>
       </c>
       <c r="H33" s="11"/>
     </row>
@@ -15415,20 +15423,20 @@
         <v>1033</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>1346</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>1347</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="10" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H34" s="11"/>
     </row>
@@ -15437,23 +15445,23 @@
         <v>1034</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>700</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>1350</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>1351</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="12" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>1352</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15461,23 +15469,23 @@
         <v>1035</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>700</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>1355</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>1356</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="12" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H36" s="10" t="s">
         <v>1352</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15485,25 +15493,25 @@
         <v>1036</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>700</v>
       </c>
       <c r="D37" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>1358</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="F37" s="10" t="s">
         <v>1359</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="G37" s="12" t="s">
         <v>1360</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="H37" s="10" t="s">
         <v>1361</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15511,25 +15519,25 @@
         <v>1037</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>700</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E38" s="10" t="s">
         <v>1364</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="10" t="s">
         <v>1365</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="G38" s="12" t="s">
         <v>1366</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="H38" s="10" t="s">
         <v>1367</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15537,23 +15545,23 @@
         <v>1038</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>700</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>1370</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>1371</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="12" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>1352</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15561,7 +15569,7 @@
         <v>1039</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>1010</v>
@@ -15572,7 +15580,7 @@
         <v>1040</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>1010</v>
@@ -15583,7 +15591,7 @@
         <v>1041</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>1010</v>
@@ -15594,7 +15602,7 @@
         <v>1042</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>1010</v>
@@ -15605,7 +15613,7 @@
         <v>1043</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>1010</v>
@@ -15616,7 +15624,7 @@
         <v>1044</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>1010</v>
@@ -15627,19 +15635,19 @@
         <v>1045</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>1010</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="G46" s="10" t="s">
         <v>1380</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -15647,7 +15655,7 @@
         <v>1046</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>1010</v>
@@ -15658,7 +15666,7 @@
         <v>1047</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>1010</v>
@@ -15669,7 +15677,7 @@
         <v>1048</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>1010</v>
@@ -15680,7 +15688,7 @@
         <v>1049</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>1010</v>
@@ -15691,7 +15699,7 @@
         <v>1050</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>1010</v>
@@ -15702,7 +15710,7 @@
         <v>1051</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>1010</v>
@@ -15747,7 +15755,7 @@
         <v>1205</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15755,7 +15763,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1389</v>
+        <v>1469</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>13</v>
@@ -15769,7 +15777,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1390</v>
+        <v>1470</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
@@ -15783,7 +15791,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1391</v>
+        <v>1471</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>13</v>
@@ -15797,7 +15805,7 @@
         <v>2013</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1392</v>
+        <v>1472</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>13</v>
@@ -15811,7 +15819,7 @@
         <v>2014</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1393</v>
+        <v>1473</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>13</v>
@@ -15825,7 +15833,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1394</v>
+        <v>1474</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>13</v>
@@ -15839,7 +15847,7 @@
         <v>2010</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1395</v>
+        <v>1475</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>13</v>
@@ -15853,7 +15861,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1396</v>
+        <v>1476</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>13</v>
@@ -15867,7 +15875,7 @@
         <v>2021</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1397</v>
+        <v>1477</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>13</v>
@@ -15881,7 +15889,7 @@
         <v>2022</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1398</v>
+        <v>1478</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>13</v>
@@ -15895,7 +15903,7 @@
         <v>2012</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1399</v>
+        <v>1479</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>13</v>
@@ -15909,7 +15917,7 @@
         <v>2011</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1400</v>
+        <v>1480</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>13</v>
@@ -15923,7 +15931,7 @@
         <v>2015</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1401</v>
+        <v>1481</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>13</v>
@@ -15937,7 +15945,7 @@
         <v>2016</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1402</v>
+        <v>1482</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>13</v>
@@ -15951,7 +15959,7 @@
         <v>2023</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1403</v>
+        <v>1483</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>13</v>
@@ -15965,7 +15973,7 @@
         <v>2024</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1404</v>
+        <v>1484</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>13</v>
@@ -15979,19 +15987,19 @@
         <v>2020</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1405</v>
+        <v>1485</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1406</v>
+        <v>1388</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15999,17 +16007,17 @@
         <v>2003</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>1411</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16017,19 +16025,19 @@
         <v>2004</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1412</v>
+        <v>1486</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1414</v>
+        <v>1395</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1415</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16037,17 +16045,17 @@
         <v>2006</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1416</v>
+        <v>1487</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1417</v>
+        <v>1397</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10" t="s">
-        <v>1418</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16055,19 +16063,19 @@
         <v>2005</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1419</v>
+        <v>1488</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1420</v>
+        <v>1399</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>1421</v>
+        <v>1400</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>1422</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16075,17 +16083,17 @@
         <v>2018</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1423</v>
+        <v>1489</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1424</v>
+        <v>1402</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10" t="s">
-        <v>1425</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16093,19 +16101,19 @@
         <v>2009</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1426</v>
+        <v>1490</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1427</v>
+        <v>1404</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1428</v>
+        <v>1405</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>1429</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16113,17 +16121,17 @@
         <v>2025</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1430</v>
+        <v>1491</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1431</v>
+        <v>1407</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10" t="s">
-        <v>1432</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16131,7 +16139,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1433</v>
+        <v>1492</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>71</v>
@@ -16140,10 +16148,10 @@
         <v>1247</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>1434</v>
+        <v>1409</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>1435</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16151,17 +16159,17 @@
         <v>2019</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1436</v>
+        <v>1493</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1437</v>
+        <v>1411</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="10" t="s">
-        <v>1438</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16169,19 +16177,19 @@
         <v>2031</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1439</v>
+        <v>1494</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1440</v>
+        <v>1413</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>1441</v>
+        <v>1414</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>1442</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16189,19 +16197,19 @@
         <v>2030</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1443</v>
+        <v>1495</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1444</v>
+        <v>1416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>1445</v>
+        <v>1417</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>1442</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16209,19 +16217,19 @@
         <v>2033</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1446</v>
+        <v>1496</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1447</v>
+        <v>1418</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>1448</v>
+        <v>1419</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>1442</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16229,19 +16237,19 @@
         <v>2032</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1449</v>
+        <v>1497</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1451</v>
+        <v>1421</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>1452</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16249,19 +16257,19 @@
         <v>2026</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1453</v>
+        <v>1498</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1454</v>
+        <v>1423</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>1455</v>
+        <v>1424</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>1456</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16269,19 +16277,19 @@
         <v>2027</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1457</v>
+        <v>1499</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1458</v>
+        <v>1426</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>1459</v>
+        <v>1427</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>1456</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16289,19 +16297,19 @@
         <v>2029</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1460</v>
+        <v>1500</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1461</v>
+        <v>1428</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>1462</v>
+        <v>1429</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>1463</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16309,14 +16317,14 @@
         <v>2028</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1464</v>
+        <v>1501</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>700</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="10" t="s">
-        <v>1465</v>
+        <v>1431</v>
       </c>
       <c r="F35" s="10"/>
     </row>
@@ -16324,8 +16332,8 @@
       <c r="A36" s="3">
         <v>2043</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>1466</v>
+      <c r="B36" s="22" t="s">
+        <v>1502</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>1010</v>
@@ -16339,14 +16347,14 @@
         <v>2040</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1467</v>
+        <v>1503</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10" t="s">
-        <v>1468</v>
+        <v>1432</v>
       </c>
       <c r="F37" s="10"/>
     </row>
@@ -16355,14 +16363,14 @@
         <v>2035</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1469</v>
+        <v>1504</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10" t="s">
-        <v>1470</v>
+        <v>1433</v>
       </c>
       <c r="F38" s="10"/>
     </row>
@@ -16371,14 +16379,14 @@
         <v>2041</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1471</v>
+        <v>1505</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10" t="s">
-        <v>1472</v>
+        <v>1434</v>
       </c>
       <c r="F39" s="10"/>
     </row>
@@ -16387,14 +16395,14 @@
         <v>2042</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1473</v>
+        <v>1506</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10" t="s">
-        <v>1474</v>
+        <v>1435</v>
       </c>
       <c r="F40" s="10"/>
     </row>
@@ -16403,14 +16411,14 @@
         <v>2044</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1475</v>
+        <v>1507</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10" t="s">
-        <v>1476</v>
+        <v>1436</v>
       </c>
       <c r="F41" s="10"/>
     </row>
@@ -16419,7 +16427,7 @@
         <v>2036</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1477</v>
+        <v>1508</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>1010</v>
@@ -16433,14 +16441,14 @@
         <v>2034</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1478</v>
+        <v>1509</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10" t="s">
-        <v>1479</v>
+        <v>1437</v>
       </c>
       <c r="F43" s="10"/>
     </row>
@@ -16449,14 +16457,14 @@
         <v>2037</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10" t="s">
-        <v>1481</v>
+        <v>1438</v>
       </c>
       <c r="F44" s="10"/>
     </row>
@@ -16465,14 +16473,14 @@
         <v>2038</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1482</v>
+        <v>1511</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10" t="s">
-        <v>1483</v>
+        <v>1439</v>
       </c>
       <c r="F45" s="10"/>
     </row>
@@ -16481,14 +16489,14 @@
         <v>2039</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1484</v>
+        <v>1512</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10" t="s">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="F46" s="10"/>
     </row>
@@ -16497,14 +16505,14 @@
         <v>2045</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10" t="s">
-        <v>1487</v>
+        <v>1441</v>
       </c>
       <c r="F47" s="10"/>
     </row>
@@ -16533,55 +16541,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1488</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1489</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1490</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1491</v>
+        <v>1445</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1492</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1493</v>
+        <v>1447</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1494</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1495</v>
+        <v>1449</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1496</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1497</v>
+        <v>1451</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1498</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1499</v>
+        <v>1453</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1500</v>
+        <v>1454</v>
       </c>
     </row>
   </sheetData>
@@ -16607,12 +16615,12 @@
         <v>1204</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>1501</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1502</v>
+        <v>1456</v>
       </c>
       <c r="B2" s="18" t="b">
         <f>FALSE()</f>
